--- a/Data/Margin_Depledge.xlsx
+++ b/Data/Margin_Depledge.xlsx
@@ -8,12 +8,12 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\abhishekyt\git\repository\Automation\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9D3D4E91-1F9C-401A-BA55-15FA5CEA38C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC288117-F64C-47B9-9621-E0673BC92C52}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="19800" windowHeight="11760" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Margin_Depledge" sheetId="1" r:id="rId1"/>
+    <sheet name="CC Depledge Request" sheetId="1" r:id="rId1"/>
     <sheet name="CM De-Pledge Request" sheetId="2" r:id="rId2"/>
     <sheet name="TM De-Pledge Request" sheetId="3" r:id="rId3"/>
   </sheets>
@@ -26,9 +26,41 @@
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="9">
+  <si>
+    <t>CC_DePledge_Request_No</t>
+  </si>
+  <si>
+    <t>CC_Client_Id_DePledge</t>
+  </si>
+  <si>
+    <t>ENWR_DePledge</t>
+  </si>
+  <si>
+    <t>De10001</t>
+  </si>
+  <si>
+    <t>CM_Client_Id</t>
+  </si>
+  <si>
+    <t>CM_pledge_Req_No</t>
+  </si>
+  <si>
+    <t>abhi222</t>
+  </si>
+  <si>
+    <t>TM_Client_Id</t>
+  </si>
+  <si>
+    <t>TM_pledge_Req_No</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -36,16 +68,45 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Consolas"/>
+      <family val="3"/>
+    </font>
+    <font>
+      <b/>
+      <i/>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Consolas"/>
+      <family val="3"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -53,12 +114,34 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="1" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -339,16 +422,79 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="C5"/>
+  <dimension ref="A1:C11"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="3" max="3" width="8" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="22.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="23.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="16.140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C5">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="7" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" s="6">
         <v>180000110000033</v>
       </c>
+      <c r="B2" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="C2" s="5"/>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" s="5"/>
+      <c r="B3" s="5"/>
+      <c r="C3" s="5"/>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" s="5"/>
+      <c r="B4" s="5"/>
+      <c r="C4" s="5"/>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" s="5"/>
+      <c r="B5" s="5"/>
+      <c r="C5" s="5"/>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6" s="5"/>
+      <c r="B6" s="5"/>
+      <c r="C6" s="5"/>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A7" s="5"/>
+      <c r="B7" s="5"/>
+      <c r="C7" s="5"/>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A8" s="5"/>
+      <c r="B8" s="5"/>
+      <c r="C8" s="5"/>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A9" s="5"/>
+      <c r="B9" s="5"/>
+      <c r="C9" s="5"/>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A10" s="5"/>
+      <c r="B10" s="5"/>
+      <c r="C10" s="5"/>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A11" s="5"/>
+      <c r="B11" s="5"/>
+      <c r="C11" s="5"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -357,18 +503,150 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2FF39B0C-DD8F-4F36-8F21-62CD61C144E1}">
-  <dimension ref="A1"/>
+  <dimension ref="A1:C10"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData/>
+  <cols>
+    <col min="1" max="1" width="16.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="17.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="16.28515625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1" s="7" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" s="3">
+        <v>100673000019391</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2" s="5"/>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" s="5"/>
+      <c r="B3" s="5"/>
+      <c r="C3" s="5"/>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" s="5"/>
+      <c r="B4" s="5"/>
+      <c r="C4" s="5"/>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" s="5"/>
+      <c r="B5" s="5"/>
+      <c r="C5" s="5"/>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6" s="5"/>
+      <c r="B6" s="5"/>
+      <c r="C6" s="5"/>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A7" s="5"/>
+      <c r="B7" s="5"/>
+      <c r="C7" s="5"/>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A8" s="5"/>
+      <c r="B8" s="5"/>
+      <c r="C8" s="5"/>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A9" s="5"/>
+      <c r="B9" s="5"/>
+      <c r="C9" s="5"/>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A10" s="5"/>
+      <c r="B10" s="5"/>
+      <c r="C10" s="5"/>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4CAAEDD9-D232-414B-866A-ABB1DD1F60EF}">
-  <dimension ref="A1"/>
+  <dimension ref="A9:C18"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData/>
+  <cols>
+    <col min="1" max="1" width="16.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="23.5703125" customWidth="1"/>
+    <col min="3" max="3" width="24.42578125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A9" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C9" s="7" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A10" s="3">
+        <v>100673000019391</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C10" s="5"/>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A11" s="5"/>
+      <c r="B11" s="5"/>
+      <c r="C11" s="5"/>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A12" s="5"/>
+      <c r="B12" s="5"/>
+      <c r="C12" s="5"/>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A13" s="5"/>
+      <c r="B13" s="5"/>
+      <c r="C13" s="5"/>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A14" s="5"/>
+      <c r="B14" s="5"/>
+      <c r="C14" s="5"/>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A15" s="5"/>
+      <c r="B15" s="5"/>
+      <c r="C15" s="5"/>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A16" s="5"/>
+      <c r="B16" s="5"/>
+      <c r="C16" s="5"/>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A17" s="5"/>
+      <c r="B17" s="5"/>
+      <c r="C17" s="5"/>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A18" s="5"/>
+      <c r="B18" s="5"/>
+      <c r="C18" s="5"/>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/Data/Margin_Depledge.xlsx
+++ b/Data/Margin_Depledge.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\abhishekyt\git\repository\Automation\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC288117-F64C-47B9-9621-E0673BC92C52}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8003DC35-7D8D-478B-952A-9DD592870D6A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="19800" windowHeight="11760" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="19800" windowHeight="11760" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="CC Depledge Request" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="11">
   <si>
     <t>CC_DePledge_Request_No</t>
   </si>
@@ -47,13 +47,19 @@
     <t>CM_pledge_Req_No</t>
   </si>
   <si>
-    <t>abhi222</t>
-  </si>
-  <si>
     <t>TM_Client_Id</t>
   </si>
   <si>
     <t>TM_pledge_Req_No</t>
+  </si>
+  <si>
+    <t>Pledge_Sequence_No</t>
+  </si>
+  <si>
+    <t>abhi1</t>
+  </si>
+  <si>
+    <t>abhi01</t>
   </si>
 </sst>
 </file>
@@ -422,79 +428,97 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C11"/>
+  <dimension ref="A1:D11"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="22.42578125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="23.42578125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="16.140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="8" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="22.42578125" customWidth="1"/>
+    <col min="3" max="3" width="23.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="16.140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="8" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="7" t="s">
         <v>1</v>
       </c>
       <c r="B1" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="C1" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="7" t="s">
+      <c r="D1" s="7" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" s="6">
         <v>180000110000033</v>
       </c>
-      <c r="B2" s="5" t="s">
+      <c r="B2" s="6">
+        <v>1150</v>
+      </c>
+      <c r="C2" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="C2" s="5"/>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D2" s="6">
+        <v>110001031605</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" s="5"/>
       <c r="B3" s="5"/>
       <c r="C3" s="5"/>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D3" s="5"/>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="5"/>
       <c r="B4" s="5"/>
       <c r="C4" s="5"/>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D4" s="5"/>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" s="5"/>
       <c r="B5" s="5"/>
       <c r="C5" s="5"/>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D5" s="5"/>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" s="5"/>
       <c r="B6" s="5"/>
       <c r="C6" s="5"/>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D6" s="5"/>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" s="5"/>
       <c r="B7" s="5"/>
       <c r="C7" s="5"/>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D7" s="5"/>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" s="5"/>
       <c r="B8" s="5"/>
       <c r="C8" s="5"/>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D8" s="5"/>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" s="5"/>
       <c r="B9" s="5"/>
       <c r="C9" s="5"/>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D9" s="5"/>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" s="5"/>
       <c r="B10" s="5"/>
       <c r="C10" s="5"/>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D10" s="5"/>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" s="5"/>
       <c r="B11" s="5"/>
       <c r="C11" s="5"/>
+      <c r="D11" s="5"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -527,9 +551,11 @@
         <v>100673000019391</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="C2" s="5"/>
+        <v>9</v>
+      </c>
+      <c r="C2" s="6">
+        <v>110001031605</v>
+      </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="5"/>
@@ -588,10 +614,10 @@
   <sheetData>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B9" s="2" t="s">
         <v>7</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>8</v>
       </c>
       <c r="C9" s="7" t="s">
         <v>2</v>
@@ -599,12 +625,14 @@
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" s="3">
-        <v>100673000019391</v>
+        <v>100673000099997</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="C10" s="5"/>
+        <v>10</v>
+      </c>
+      <c r="C10" s="6">
+        <v>110001031605</v>
+      </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" s="5"/>

--- a/Data/Margin_Depledge.xlsx
+++ b/Data/Margin_Depledge.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\abhishekyt\git\repository\Automation\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8003DC35-7D8D-478B-952A-9DD592870D6A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9FAFBA2F-5D7A-4C14-8998-F4A9F3E89407}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="19800" windowHeight="11760" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="19800" windowHeight="11760" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="CC Depledge Request" sheetId="1" r:id="rId1"/>
@@ -38,9 +38,6 @@
     <t>ENWR_DePledge</t>
   </si>
   <si>
-    <t>De10001</t>
-  </si>
-  <si>
     <t>CM_Client_Id</t>
   </si>
   <si>
@@ -56,10 +53,13 @@
     <t>Pledge_Sequence_No</t>
   </si>
   <si>
-    <t>abhi1</t>
-  </si>
-  <si>
-    <t>abhi01</t>
+    <t>De10003</t>
+  </si>
+  <si>
+    <t>abhi3</t>
+  </si>
+  <si>
+    <t>abhi03</t>
   </si>
 </sst>
 </file>
@@ -443,7 +443,7 @@
         <v>1</v>
       </c>
       <c r="B1" s="7" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C1" s="7" t="s">
         <v>0</v>
@@ -457,13 +457,13 @@
         <v>180000110000033</v>
       </c>
       <c r="B2" s="6">
-        <v>1150</v>
+        <v>1154</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="D2" s="6">
-        <v>110001031605</v>
+        <v>110001031563</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
@@ -537,10 +537,10 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1" s="2" t="s">
         <v>4</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>5</v>
       </c>
       <c r="C1" s="7" t="s">
         <v>2</v>
@@ -554,7 +554,7 @@
         <v>9</v>
       </c>
       <c r="C2" s="6">
-        <v>110001031605</v>
+        <v>110001031563</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
@@ -604,7 +604,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4CAAEDD9-D232-414B-866A-ABB1DD1F60EF}">
-  <dimension ref="A9:C18"/>
+  <dimension ref="A1:C18"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="16.140625" bestFit="1" customWidth="1"/>
@@ -612,27 +612,67 @@
     <col min="3" max="3" width="24.42578125" customWidth="1"/>
   </cols>
   <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C1" s="7" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" s="3">
+        <v>100673000099997</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C2" s="6">
+        <v>110001031563</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" s="5"/>
+      <c r="B3" s="5"/>
+      <c r="C3" s="5"/>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" s="5"/>
+      <c r="B4" s="5"/>
+      <c r="C4" s="5"/>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" s="5"/>
+      <c r="B5" s="5"/>
+      <c r="C5" s="5"/>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6" s="5"/>
+      <c r="B6" s="5"/>
+      <c r="C6" s="5"/>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A7" s="5"/>
+      <c r="B7" s="5"/>
+      <c r="C7" s="5"/>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A8" s="5"/>
+      <c r="B8" s="5"/>
+      <c r="C8" s="5"/>
+    </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A9" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C9" s="7" t="s">
-        <v>2</v>
-      </c>
+      <c r="A9" s="5"/>
+      <c r="B9" s="5"/>
+      <c r="C9" s="5"/>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A10" s="3">
-        <v>100673000099997</v>
-      </c>
-      <c r="B10" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="C10" s="6">
-        <v>110001031605</v>
-      </c>
+      <c r="A10" s="5"/>
+      <c r="B10" s="5"/>
+      <c r="C10" s="5"/>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" s="5"/>

--- a/Data/Margin_Depledge.xlsx
+++ b/Data/Margin_Depledge.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\abhishekyt\git\repository\Automation\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9FAFBA2F-5D7A-4C14-8998-F4A9F3E89407}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{926640E1-12CB-4DDA-BFC3-E1847402D565}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="19800" windowHeight="11760" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="22">
   <si>
     <t>CC_DePledge_Request_No</t>
   </si>
@@ -56,17 +56,50 @@
     <t>De10003</t>
   </si>
   <si>
-    <t>abhi3</t>
-  </si>
-  <si>
     <t>abhi03</t>
+  </si>
+  <si>
+    <t>abhi4</t>
+  </si>
+  <si>
+    <t>abhi5</t>
+  </si>
+  <si>
+    <t>abhi6</t>
+  </si>
+  <si>
+    <t>abhi7</t>
+  </si>
+  <si>
+    <t>abhi8</t>
+  </si>
+  <si>
+    <t>abhi9</t>
+  </si>
+  <si>
+    <t>De10004</t>
+  </si>
+  <si>
+    <t>abhi04</t>
+  </si>
+  <si>
+    <t>abhi05</t>
+  </si>
+  <si>
+    <t>abhi10</t>
+  </si>
+  <si>
+    <t>abhi11</t>
+  </si>
+  <si>
+    <t>abhi901</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -96,6 +129,18 @@
       <color theme="1"/>
       <name val="Consolas"/>
       <family val="3"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF2A314A"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="3">
@@ -139,7 +184,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -148,6 +193,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="1" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -467,10 +513,18 @@
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A3" s="5"/>
-      <c r="B3" s="5"/>
-      <c r="C3" s="5"/>
-      <c r="D3" s="5"/>
+      <c r="A3" s="6">
+        <v>180000110000033</v>
+      </c>
+      <c r="B3" s="5">
+        <v>1157</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="D3" s="6">
+        <v>110001031605</v>
+      </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="5"/>
@@ -521,13 +575,14 @@
       <c r="D11" s="5"/>
     </row>
   </sheetData>
+  <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2FF39B0C-DD8F-4F36-8F21-62CD61C144E1}">
-  <dimension ref="A1:C10"/>
+  <dimension ref="A1:D11"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="16.140625" bestFit="1" customWidth="1"/>
@@ -535,7 +590,7 @@
     <col min="3" max="3" width="16.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>3</v>
       </c>
@@ -546,58 +601,110 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" s="3">
-        <v>100673000019391</v>
+        <v>180000110000033</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="C2" s="6">
-        <v>110001031563</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3" s="5"/>
-      <c r="B3" s="5"/>
-      <c r="C3" s="5"/>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4" s="5"/>
-      <c r="B4" s="5"/>
-      <c r="C4" s="5"/>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5" s="5"/>
-      <c r="B5" s="5"/>
-      <c r="C5" s="5"/>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A6" s="5"/>
-      <c r="B6" s="5"/>
-      <c r="C6" s="5"/>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A7" s="5"/>
-      <c r="B7" s="5"/>
-      <c r="C7" s="5"/>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A8" s="5"/>
-      <c r="B8" s="5"/>
-      <c r="C8" s="5"/>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A9" s="5"/>
-      <c r="B9" s="5"/>
-      <c r="C9" s="5"/>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A10" s="5"/>
-      <c r="B10" s="5"/>
-      <c r="C10" s="5"/>
+        <v>110001032140</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A3" s="6">
+        <v>120733340001651</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C3" s="6">
+        <v>110001031605</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A4" s="6">
+        <v>120733340001651</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C4" s="8">
+        <v>110001032140</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A5" s="6">
+        <v>120733340001651</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C5" s="8">
+        <v>110001032165</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A6" s="6">
+        <v>120733340001651</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="C6" s="8">
+        <v>110001032124</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A7" s="6">
+        <v>120733340001651</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C7" s="8">
+        <v>110001032108</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A8" s="6">
+        <v>120733340001651</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C8" s="8">
+        <v>110001032181</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A9" s="6">
+        <v>120733340001651</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="C9" s="8">
+        <v>110001032207</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A10" s="6">
+        <v>120733340001651</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="C10" s="8">
+        <v>110001032223</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="D11" s="5"/>
     </row>
   </sheetData>
+  <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -628,20 +735,28 @@
         <v>100673000099997</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C2" s="6">
         <v>110001031563</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3" s="5"/>
-      <c r="B3" s="5"/>
-      <c r="C3" s="5"/>
+      <c r="A3" s="6">
+        <v>155000010007402</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="C3" s="6">
+        <v>110001031605</v>
+      </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="5"/>
-      <c r="B4" s="5"/>
+      <c r="B4" s="4" t="s">
+        <v>18</v>
+      </c>
       <c r="C4" s="5"/>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
@@ -715,6 +830,7 @@
       <c r="C18" s="5"/>
     </row>
   </sheetData>
+  <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/Data/Margin_Depledge.xlsx
+++ b/Data/Margin_Depledge.xlsx
@@ -8,14 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\abhishekyt\git\repository\Automation\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{926640E1-12CB-4DDA-BFC3-E1847402D565}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9D6D7AC2-1216-4FD5-BFE9-9770B9DD6F37}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="19800" windowHeight="11760" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="19800" windowHeight="11760" firstSheet="1" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="CC Depledge Request" sheetId="1" r:id="rId1"/>
     <sheet name="CM De-Pledge Request" sheetId="2" r:id="rId2"/>
     <sheet name="TM De-Pledge Request" sheetId="3" r:id="rId3"/>
+    <sheet name="RP_Margin_DePledge_Request" sheetId="4" r:id="rId4"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -27,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="28">
   <si>
     <t>CC_DePledge_Request_No</t>
   </si>
@@ -56,9 +57,6 @@
     <t>De10003</t>
   </si>
   <si>
-    <t>abhi03</t>
-  </si>
-  <si>
     <t>abhi4</t>
   </si>
   <si>
@@ -92,7 +90,28 @@
     <t>abhi11</t>
   </si>
   <si>
-    <t>abhi901</t>
+    <t>RP_Client_Id_DePledge</t>
+  </si>
+  <si>
+    <t>RP_Pledge_Sequence_No</t>
+  </si>
+  <si>
+    <t>RP_DePledge_Request_No</t>
+  </si>
+  <si>
+    <t>RP_ENWR_DePledge</t>
+  </si>
+  <si>
+    <t>TM_Client_Id_DePledge</t>
+  </si>
+  <si>
+    <t>CC_Client_Id</t>
+  </si>
+  <si>
+    <t>abhi902</t>
+  </si>
+  <si>
+    <t>Ru12</t>
   </si>
 </sst>
 </file>
@@ -143,7 +162,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -153,6 +172,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="4" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -184,7 +209,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -194,6 +219,9 @@
     <xf numFmtId="1" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="1" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="1" fontId="1" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="1" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -520,7 +548,7 @@
         <v>1157</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D3" s="6">
         <v>110001031605</v>
@@ -582,126 +610,159 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2FF39B0C-DD8F-4F36-8F21-62CD61C144E1}">
-  <dimension ref="A1:D11"/>
+  <dimension ref="A1:E11"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="16.140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="17.85546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="16.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.140625" customWidth="1"/>
+    <col min="3" max="3" width="17.85546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="16.28515625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="23.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="C1" s="7" t="s">
+      <c r="D1" s="7" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E1" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="3">
+        <v>120733340001651</v>
+      </c>
+      <c r="B2" s="6">
+        <v>1158</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="D2" s="11">
+        <v>110001032165</v>
+      </c>
+      <c r="E2" s="6">
         <v>180000110000033</v>
       </c>
-      <c r="B2" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="C2" s="6">
-        <v>110001032140</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" s="6">
         <v>120733340001651</v>
       </c>
-      <c r="B3" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="C3" s="6">
+      <c r="B3" s="5">
+        <v>1157</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="D3" s="6">
         <v>110001031605</v>
       </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E3" s="5"/>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="6">
         <v>120733340001651</v>
       </c>
-      <c r="B4" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="C4" s="8">
+      <c r="B4" s="5"/>
+      <c r="C4" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="D4" s="8">
         <v>110001032140</v>
       </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E4" s="5"/>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="6">
         <v>120733340001651</v>
       </c>
-      <c r="B5" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="C5" s="8">
+      <c r="B5" s="5"/>
+      <c r="C5" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D5" s="8">
         <v>110001032165</v>
       </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E5" s="5"/>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="6">
         <v>120733340001651</v>
       </c>
-      <c r="B6" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="C6" s="8">
+      <c r="B6" s="5"/>
+      <c r="C6" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="D6" s="8">
         <v>110001032124</v>
       </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E6" s="5"/>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="6">
         <v>120733340001651</v>
       </c>
-      <c r="B7" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="C7" s="8">
+      <c r="B7" s="5"/>
+      <c r="C7" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="D7" s="8">
         <v>110001032108</v>
       </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E7" s="5"/>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="6">
         <v>120733340001651</v>
       </c>
-      <c r="B8" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="C8" s="8">
+      <c r="B8" s="5"/>
+      <c r="C8" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D8" s="8">
         <v>110001032181</v>
       </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E8" s="5"/>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="6">
         <v>120733340001651</v>
       </c>
-      <c r="B9" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="C9" s="8">
+      <c r="B9" s="5"/>
+      <c r="C9" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="D9" s="8">
         <v>110001032207</v>
       </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E9" s="5"/>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" s="6">
         <v>120733340001651</v>
       </c>
-      <c r="B10" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="C10" s="8">
+      <c r="B10" s="5"/>
+      <c r="C10" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="D10" s="8">
         <v>110001032223</v>
       </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="D11" s="5"/>
+      <c r="E10" s="5"/>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B11" s="5"/>
+      <c r="E11" s="5"/>
     </row>
   </sheetData>
   <phoneticPr fontId="4" type="noConversion"/>
@@ -711,15 +772,16 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4CAAEDD9-D232-414B-866A-ABB1DD1F60EF}">
-  <dimension ref="A1:C18"/>
+  <dimension ref="A1:D18"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="16.140625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="23.5703125" customWidth="1"/>
     <col min="3" max="3" width="24.42578125" customWidth="1"/>
+    <col min="4" max="4" width="23.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>5</v>
       </c>
@@ -729,108 +791,251 @@
       <c r="C1" s="7" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" s="3">
-        <v>100673000099997</v>
+        <v>155000010007402</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="C2" s="6">
-        <v>110001031563</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+        <v>110001032165</v>
+      </c>
+      <c r="D2" s="6">
+        <v>120733340001651</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" s="6">
         <v>155000010007402</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C3" s="6">
         <v>110001031605</v>
       </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D3" s="5"/>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="5"/>
       <c r="B4" s="4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C4" s="5"/>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D4" s="5"/>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" s="5"/>
       <c r="B5" s="5"/>
       <c r="C5" s="5"/>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D5" s="5"/>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" s="5"/>
       <c r="B6" s="5"/>
       <c r="C6" s="5"/>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D6" s="5"/>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" s="5"/>
       <c r="B7" s="5"/>
       <c r="C7" s="5"/>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D7" s="5"/>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" s="5"/>
       <c r="B8" s="5"/>
       <c r="C8" s="5"/>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D8" s="5"/>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" s="5"/>
       <c r="B9" s="5"/>
       <c r="C9" s="5"/>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D9" s="5"/>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" s="5"/>
       <c r="B10" s="5"/>
       <c r="C10" s="5"/>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D10" s="5"/>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" s="5"/>
       <c r="B11" s="5"/>
       <c r="C11" s="5"/>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D11" s="5"/>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" s="5"/>
       <c r="B12" s="5"/>
       <c r="C12" s="5"/>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D12" s="5"/>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" s="5"/>
       <c r="B13" s="5"/>
       <c r="C13" s="5"/>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D13" s="5"/>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" s="5"/>
       <c r="B14" s="5"/>
       <c r="C14" s="5"/>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D14" s="5"/>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" s="5"/>
       <c r="B15" s="5"/>
       <c r="C15" s="5"/>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D15" s="5"/>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" s="5"/>
       <c r="B16" s="5"/>
       <c r="C16" s="5"/>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D16" s="5"/>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" s="5"/>
       <c r="B17" s="5"/>
       <c r="C17" s="5"/>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D17" s="5"/>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" s="5"/>
       <c r="B18" s="5"/>
       <c r="C18" s="5"/>
+      <c r="D18" s="5"/>
     </row>
   </sheetData>
   <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B0539182-0F9A-4E25-992D-B2CD09E3B975}">
+  <dimension ref="A1:E12"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="22.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="20.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="25.140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="19.7109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="28.140625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="B1" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="C1" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="D1" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="E1" s="7" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2" s="3">
+        <v>155000010007402</v>
+      </c>
+      <c r="B2" s="4">
+        <v>1158</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="D2" s="3">
+        <v>110001032165</v>
+      </c>
+      <c r="E2" s="9">
+        <v>100673000000011</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3" s="5"/>
+      <c r="B3" s="5"/>
+      <c r="C3" s="5"/>
+      <c r="D3" s="5"/>
+      <c r="E3" s="5"/>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4" s="5"/>
+      <c r="B4" s="5"/>
+      <c r="C4" s="5"/>
+      <c r="D4" s="5"/>
+      <c r="E4" s="5"/>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A5" s="5"/>
+      <c r="B5" s="5"/>
+      <c r="C5" s="5"/>
+      <c r="D5" s="5"/>
+      <c r="E5" s="5"/>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A6" s="5"/>
+      <c r="B6" s="5"/>
+      <c r="C6" s="5"/>
+      <c r="D6" s="5"/>
+      <c r="E6" s="5"/>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A7" s="5"/>
+      <c r="B7" s="5"/>
+      <c r="C7" s="5"/>
+      <c r="D7" s="5"/>
+      <c r="E7" s="5"/>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A8" s="5"/>
+      <c r="B8" s="5"/>
+      <c r="C8" s="5"/>
+      <c r="D8" s="5"/>
+      <c r="E8" s="5"/>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A9" s="5"/>
+      <c r="B9" s="5"/>
+      <c r="C9" s="5"/>
+      <c r="D9" s="5"/>
+      <c r="E9" s="5"/>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A10" s="5"/>
+      <c r="B10" s="5"/>
+      <c r="C10" s="5"/>
+      <c r="D10" s="5"/>
+      <c r="E10" s="5"/>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A11" s="5"/>
+      <c r="B11" s="5"/>
+      <c r="C11" s="5"/>
+      <c r="D11" s="5"/>
+      <c r="E11" s="5"/>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A12" s="5"/>
+      <c r="B12" s="5"/>
+      <c r="C12" s="5"/>
+      <c r="D12" s="5"/>
+      <c r="E12" s="5"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>